--- a/03_Outputs/Vulnerable_ref_subset/04_Cluster/Summary_Stats.xlsx
+++ b/03_Outputs/Vulnerable_ref_subset/04_Cluster/Summary_Stats.xlsx
@@ -406,7 +406,7 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>-1.978869742966135E-17</v>
+        <v>-1.981580248397349E-17</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -433,7 +433,7 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>1.586950735430635E-17</v>
+        <v>1.592170968112972E-17</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -460,7 +460,7 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>-2.261163864172546E-17</v>
+        <v>-2.261565420532726E-17</v>
       </c>
       <c r="E4">
         <v>0.9999999999999999</v>
@@ -487,7 +487,7 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>3.626053932423743E-17</v>
+        <v>3.623644594262664E-17</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -514,7 +514,7 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>2.136480614336713E-17</v>
+        <v>2.134673610715904E-17</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -541,7 +541,7 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>-3.086964518882339E-17</v>
+        <v>-3.088771522503148E-17</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -568,7 +568,7 @@
         <v>27</v>
       </c>
       <c r="D8">
-        <v>4.592198535016381E-17</v>
+        <v>4.591094255025886E-17</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -595,7 +595,7 @@
         <v>27</v>
       </c>
       <c r="D9">
-        <v>3.259031419219391E-17</v>
+        <v>3.25943297557957E-17</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -622,7 +622,7 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>4.590993865935842E-17</v>
+        <v>4.590717795938218E-17</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -649,7 +649,7 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>1.617669796984391E-17</v>
+        <v>1.621359096043543E-17</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -676,7 +676,7 @@
         <v>27</v>
       </c>
       <c r="D12">
-        <v>8.907423570598733E-17</v>
+        <v>8.908126294229049E-17</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -703,7 +703,7 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>-3.185948161666664E-17</v>
+        <v>-3.184341936225944E-17</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -757,7 +757,7 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>-3.288345033512517E-17</v>
+        <v>-3.285534138991258E-17</v>
       </c>
       <c r="E15">
         <v>0.9999999999999999</v>
@@ -784,7 +784,7 @@
         <v>27</v>
       </c>
       <c r="D16">
-        <v>-5.731765290661678E-17</v>
+        <v>-5.733823267007599E-17</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -811,7 +811,7 @@
         <v>27</v>
       </c>
       <c r="D17">
-        <v>-8.761959779123595E-18</v>
+        <v>-8.769990906327191E-18</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -838,7 +838,7 @@
         <v>27</v>
       </c>
       <c r="D18">
-        <v>-2.063999691324257E-18</v>
+        <v>-2.039906309713467E-18</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -865,7 +865,7 @@
         <v>27</v>
       </c>
       <c r="D19">
-        <v>1.207166259154318E-17</v>
+        <v>1.205070636899629E-17</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -892,7 +892,7 @@
         <v>27</v>
       </c>
       <c r="D20">
-        <v>2.177690335800167E-17</v>
+        <v>2.182860373937482E-17</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -919,7 +919,7 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>7.429194219686784E-17</v>
+        <v>7.431603557847863E-17</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -946,7 +946,7 @@
         <v>27</v>
       </c>
       <c r="D22">
-        <v>2.285257245783335E-17</v>
+        <v>2.284855689423156E-17</v>
       </c>
       <c r="E22">
         <v>0.9999999999999999</v>
@@ -973,7 +973,7 @@
         <v>27</v>
       </c>
       <c r="D23">
-        <v>2.047937436917064E-18</v>
+        <v>2.043921873315266E-18</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1000,7 +1000,7 @@
         <v>27</v>
       </c>
       <c r="D24">
-        <v>8.312216655722201E-18</v>
+        <v>8.320247782925798E-18</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -1027,7 +1027,7 @@
         <v>27</v>
       </c>
       <c r="D25">
-        <v>2.71211165665448E-17</v>
+        <v>2.71291476937484E-17</v>
       </c>
       <c r="E25">
         <v>0.9999999999999999</v>
@@ -1054,7 +1054,7 @@
         <v>27</v>
       </c>
       <c r="D26">
-        <v>-2.620054861083258E-17</v>
+        <v>-2.622263421064246E-17</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -1081,7 +1081,7 @@
         <v>27</v>
       </c>
       <c r="D27">
-        <v>-6.03940765710444E-17</v>
+        <v>-6.045029446146957E-17</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -1108,7 +1108,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>1.926667416142759E-17</v>
+        <v>1.92506119070204E-17</v>
       </c>
       <c r="E28">
         <v>0.9999999999999999</v>
@@ -1135,7 +1135,7 @@
         <v>27</v>
       </c>
       <c r="D29">
-        <v>7.299340931713636E-17</v>
+        <v>7.300294628069064E-17</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -1162,7 +1162,7 @@
         <v>27</v>
       </c>
       <c r="D30">
-        <v>6.477104089700439E-18</v>
+        <v>6.473088526098641E-18</v>
       </c>
       <c r="E30">
         <v>0.9999999999999999</v>
@@ -1216,7 +1216,7 @@
         <v>27</v>
       </c>
       <c r="D32">
-        <v>2.834987902869504E-18</v>
+        <v>2.858579339030068E-18</v>
       </c>
       <c r="E32">
         <v>0.9999999999999999</v>
@@ -1243,7 +1243,7 @@
         <v>27</v>
       </c>
       <c r="D33">
-        <v>1.862257775969917E-16</v>
+        <v>1.862418398513989E-16</v>
       </c>
       <c r="E33">
         <v>0.9999999999999999</v>

--- a/03_Outputs/Vulnerable_ref_subset/04_Cluster/Summary_Stats.xlsx
+++ b/03_Outputs/Vulnerable_ref_subset/04_Cluster/Summary_Stats.xlsx
@@ -406,7 +406,7 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>-1.981580248397349E-17</v>
+        <v>-7.053337466558476E-18</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -415,7 +415,7 @@
         <v>-4.9383942253109</v>
       </c>
       <c r="G2">
-        <v>0.3705760242498868</v>
+        <v>0.3705760242498871</v>
       </c>
     </row>
     <row r="3">
@@ -433,16 +433,16 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>1.592170968112972E-17</v>
+        <v>-3.159043885534616E-17</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>-1.498554868016282</v>
+        <v>-1.498554868016283</v>
       </c>
       <c r="G3">
-        <v>2.098246189275386</v>
+        <v>2.098246189275385</v>
       </c>
     </row>
     <row r="4">
@@ -460,16 +460,16 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>-2.261565420532726E-17</v>
+        <v>-3.112061791393577E-18</v>
       </c>
       <c r="E4">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>-1.805232252045457</v>
+        <v>-1.805232252045454</v>
       </c>
       <c r="G4">
-        <v>2.250067821606941</v>
+        <v>2.250067821606944</v>
       </c>
     </row>
     <row r="5">
@@ -487,16 +487,16 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>3.623644594262664E-17</v>
+        <v>4.601835887660697E-17</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F5">
         <v>-2.51826322605039</v>
       </c>
       <c r="G5">
-        <v>1.721040880455245</v>
+        <v>1.721040880455246</v>
       </c>
     </row>
     <row r="6">
@@ -514,13 +514,13 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>2.134673610715904E-17</v>
+        <v>-1.105886215935215E-17</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F6">
-        <v>-2.209468441011076</v>
+        <v>-2.209468441011078</v>
       </c>
       <c r="G6">
         <v>1.904738775024928</v>
@@ -541,16 +541,16 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>-3.088771522503148E-17</v>
+        <v>2.265580984134524E-17</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F7">
-        <v>-2.034662498324392</v>
+        <v>-2.034662498324389</v>
       </c>
       <c r="G7">
-        <v>1.514334482697379</v>
+        <v>1.514334482697383</v>
       </c>
     </row>
     <row r="8">
@@ -568,16 +568,16 @@
         <v>27</v>
       </c>
       <c r="D8">
-        <v>4.591094255025886E-17</v>
+        <v>6.791321941541145E-18</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F8">
-        <v>-2.06357804893308</v>
+        <v>-2.063578048933079</v>
       </c>
       <c r="G8">
-        <v>1.534841272192283</v>
+        <v>1.534841272192282</v>
       </c>
     </row>
     <row r="9">
@@ -595,13 +595,13 @@
         <v>27</v>
       </c>
       <c r="D9">
-        <v>3.25943297557957E-17</v>
+        <v>-1.719865890650154E-17</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>-2.991364154966453</v>
+        <v>-2.991364154966454</v>
       </c>
       <c r="G9">
         <v>1.923590749186944</v>
@@ -622,13 +622,13 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>4.590717795938218E-17</v>
+        <v>-7.846461472458636E-17</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>-2.424285023594978</v>
+        <v>-2.424285023594979</v>
       </c>
       <c r="G10">
         <v>1.464298282069075</v>
@@ -649,13 +649,13 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>1.621359096043543E-17</v>
+        <v>1.643294112218365E-17</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11">
-        <v>-1.981878205570039</v>
+        <v>-1.98187820557004</v>
       </c>
       <c r="G11">
         <v>2.148454236051425</v>
@@ -676,16 +676,16 @@
         <v>27</v>
       </c>
       <c r="D12">
-        <v>8.908126294229049E-17</v>
+        <v>-9.083204867267449E-17</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F12">
         <v>-2.366890330932922</v>
       </c>
       <c r="G12">
-        <v>1.861170060072352</v>
+        <v>1.861170060072351</v>
       </c>
     </row>
     <row r="13">
@@ -703,16 +703,16 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>-3.184341936225944E-17</v>
+        <v>3.852130163204979E-17</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13">
-        <v>-1.742986736818007</v>
+        <v>-1.742986736818005</v>
       </c>
       <c r="G13">
-        <v>2.283851047934908</v>
+        <v>2.28385104793491</v>
       </c>
     </row>
     <row r="14">
@@ -730,16 +730,16 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>-3.626053932423743E-17</v>
+        <v>-2.570763817871185E-17</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F14">
-        <v>-2.067930763104719</v>
+        <v>-2.067930763104718</v>
       </c>
       <c r="G14">
-        <v>1.499781079856375</v>
+        <v>1.499781079856379</v>
       </c>
     </row>
     <row r="15">
@@ -757,13 +757,13 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>-3.285534138991258E-17</v>
+        <v>1.99171954649189E-18</v>
       </c>
       <c r="E15">
         <v>0.9999999999999999</v>
       </c>
       <c r="F15">
-        <v>-1.501271084975932</v>
+        <v>-1.501271084975931</v>
       </c>
       <c r="G15">
         <v>2.493912516927164</v>
@@ -784,13 +784,13 @@
         <v>27</v>
       </c>
       <c r="D16">
-        <v>-5.733823267007599E-17</v>
+        <v>5.170439693675317E-17</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16">
-        <v>-2.805193760505846</v>
+        <v>-2.805193760505845</v>
       </c>
       <c r="G16">
         <v>1.818396134464122</v>
@@ -811,16 +811,16 @@
         <v>27</v>
       </c>
       <c r="D17">
-        <v>-8.769990906327191E-18</v>
+        <v>-1.638349949533651E-18</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F17">
-        <v>-1.117328723115864</v>
+        <v>-1.117328723115865</v>
       </c>
       <c r="G17">
-        <v>2.781370592124974</v>
+        <v>2.781370592124971</v>
       </c>
     </row>
     <row r="18">
@@ -838,16 +838,16 @@
         <v>27</v>
       </c>
       <c r="D18">
-        <v>-2.039906309713467E-18</v>
+        <v>3.469446951953614E-18</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18">
-        <v>-1.731665926746751</v>
+        <v>-1.731665926746749</v>
       </c>
       <c r="G18">
-        <v>2.607087746251885</v>
+        <v>2.60708774625189</v>
       </c>
     </row>
     <row r="19">
@@ -865,16 +865,16 @@
         <v>27</v>
       </c>
       <c r="D19">
-        <v>1.205070636899629E-17</v>
+        <v>-1.898960027290352E-17</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19">
-        <v>-2.285304052127429</v>
+        <v>-2.285304052127425</v>
       </c>
       <c r="G19">
-        <v>2.926059110057242</v>
+        <v>2.926059110057244</v>
       </c>
     </row>
     <row r="20">
@@ -892,16 +892,16 @@
         <v>27</v>
       </c>
       <c r="D20">
-        <v>2.182860373937482E-17</v>
+        <v>-4.864855303578477E-18</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F20">
-        <v>-2.74425882357251</v>
+        <v>-2.744258823572514</v>
       </c>
       <c r="G20">
-        <v>1.623576492009126</v>
+        <v>1.623576492009128</v>
       </c>
     </row>
     <row r="21">
@@ -919,16 +919,16 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>7.431603557847863E-17</v>
+        <v>-1.185293986160773E-16</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F21">
-        <v>-3.195411011719337</v>
+        <v>-3.195411011719339</v>
       </c>
       <c r="G21">
-        <v>1.948808293024876</v>
+        <v>1.948808293024874</v>
       </c>
     </row>
     <row r="22">
@@ -946,16 +946,16 @@
         <v>27</v>
       </c>
       <c r="D22">
-        <v>2.284855689423156E-17</v>
+        <v>-5.257175867474157E-17</v>
       </c>
       <c r="E22">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>-2.886090386468603</v>
+        <v>-2.8860903864686</v>
       </c>
       <c r="G22">
-        <v>1.583540540954407</v>
+        <v>1.583540540954409</v>
       </c>
     </row>
     <row r="23">
@@ -973,7 +973,7 @@
         <v>27</v>
       </c>
       <c r="D23">
-        <v>2.043921873315266E-18</v>
+        <v>-3.442442286731521E-17</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -982,7 +982,7 @@
         <v>-1.850231698356104</v>
       </c>
       <c r="G23">
-        <v>2.562095472075564</v>
+        <v>2.562095472075568</v>
       </c>
     </row>
     <row r="24">
@@ -1000,16 +1000,16 @@
         <v>27</v>
       </c>
       <c r="D24">
-        <v>8.320247782925798E-18</v>
+        <v>-6.806380305047889E-18</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24">
-        <v>-2.398159283153091</v>
+        <v>-2.398159283153053</v>
       </c>
       <c r="G24">
-        <v>2.068798807824929</v>
+        <v>2.068798807824872</v>
       </c>
     </row>
     <row r="25">
@@ -1027,13 +1027,13 @@
         <v>27</v>
       </c>
       <c r="D25">
-        <v>2.71291476937484E-17</v>
+        <v>-6.182361721328454E-17</v>
       </c>
       <c r="E25">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>-1.732220849965984</v>
+        <v>-1.732220849965983</v>
       </c>
       <c r="G25">
         <v>2.063969932071146</v>
@@ -1054,16 +1054,16 @@
         <v>27</v>
       </c>
       <c r="D26">
-        <v>-2.622263421064246E-17</v>
+        <v>-3.633081168726889E-18</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>-1.538734159972581</v>
+        <v>-1.538734159972582</v>
       </c>
       <c r="G26">
-        <v>1.805321519497481</v>
+        <v>1.80532151949748</v>
       </c>
     </row>
     <row r="27">
@@ -1081,16 +1081,16 @@
         <v>27</v>
       </c>
       <c r="D27">
-        <v>-6.045029446146957E-17</v>
+        <v>-6.789514937920336E-17</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27">
-        <v>-3.057529982695132</v>
+        <v>-3.057529982695131</v>
       </c>
       <c r="G27">
-        <v>1.337909691791736</v>
+        <v>1.337909691791737</v>
       </c>
     </row>
     <row r="28">
@@ -1108,10 +1108,10 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>1.92506119070204E-17</v>
+        <v>-9.27595192015376E-18</v>
       </c>
       <c r="E28">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F28">
         <v>-2.410788490907607</v>
@@ -1135,7 +1135,7 @@
         <v>27</v>
       </c>
       <c r="D29">
-        <v>7.300294628069064E-17</v>
+        <v>1.441185776685361E-17</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -1162,13 +1162,13 @@
         <v>27</v>
       </c>
       <c r="D30">
-        <v>6.473088526098641E-18</v>
+        <v>1.305660505124673E-17</v>
       </c>
       <c r="E30">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>-2.473943862785645</v>
+        <v>-2.473943862785646</v>
       </c>
       <c r="G30">
         <v>1.409168088745029</v>
@@ -1189,16 +1189,16 @@
         <v>27</v>
       </c>
       <c r="D31">
-        <v>-1.514670590598268E-17</v>
+        <v>-3.642116186830936E-18</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F31">
         <v>-2.42711014155145</v>
       </c>
       <c r="G31">
-        <v>1.413314687191804</v>
+        <v>1.413314687191805</v>
       </c>
     </row>
     <row r="32">
@@ -1216,7 +1216,7 @@
         <v>27</v>
       </c>
       <c r="D32">
-        <v>2.858579339030068E-18</v>
+        <v>3.34250494759177E-17</v>
       </c>
       <c r="E32">
         <v>0.9999999999999999</v>
@@ -1243,16 +1243,16 @@
         <v>27</v>
       </c>
       <c r="D33">
-        <v>1.862418398513989E-16</v>
+        <v>8.470831417993228E-17</v>
       </c>
       <c r="E33">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>-1.844393609144736</v>
+        <v>-2.185212677083582</v>
       </c>
       <c r="G33">
-        <v>2.944931664630468</v>
+        <v>2.764176958516343</v>
       </c>
     </row>
   </sheetData>
